--- a/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nano_recruitment_milestones_latest.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
